--- a/student_assessment_forms/007_integer_comparison_quiz--student_assessment_forms.xlsx
+++ b/student_assessment_forms/007_integer_comparison_quiz--student_assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>compare_first</t>
+          <t>Compare the two integers on the first pair of numbers.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>compare_second</t>
+          <t>Compare the two integers on the second pair of numbers.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>correct_answer</t>
+          <t>correct_answer_first_int</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>correct_answer</t>
+          <t>What is the correct answer for the first pair of numbers?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,18 +589,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>question_type</t>
+          <t>question_type_first</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>question_type</t>
+          <t>What is the type of question being asked for the first pair of numbers?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +612,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>correct_answer_type</t>
+          <t>correct_answer_type_first</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>correct_answer_type</t>
+          <t>What is the correct answer type for the first pair of numbers?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,41 +635,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>feedback_first</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>What is your feedback on the first pair of numbers?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>correct_answer</t>
+          <t>compare_third_int</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>correct_answer</t>
+          <t>Compare the two integers on the third pair of numbers.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,41 +681,41 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>compare_fourth_int</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>Compare the two integers on the fourth pair of numbers.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>submit_text</t>
+          <t>correct_answer_fourth</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>What is the correct answer for the fourth pair of numbers?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,64 +727,64 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>question_type_fourth</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>What is the type of question being asked for the fourth pair of numbers?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>feedback_text</t>
+          <t>correct_answer_type_fourth</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>What is the correct answer type for the fourth pair of numbers?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>correct_question_type</t>
+          <t>feedback_fourth</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>correct_question_type</t>
+          <t>What is your feedback on the fourth pair of numbers?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -799,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>very_similar</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Very Similar</t>
         </is>
       </c>
     </row>
@@ -849,29 +849,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>somewhat_similar</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Somewhat Similar</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>compare_second_int_choices</t>
+          <t>compare_first_int_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>not_similar</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not Similar</t>
         </is>
       </c>
     </row>
@@ -883,250 +883,386 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>very_similar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Very Similar</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>correct_answer_choices</t>
+          <t>compare_second_int_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>somewhat_similar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Somewhat Similar</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>correct_answer_choices</t>
+          <t>compare_second_int_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>not_similar</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not Similar</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question_type_choices</t>
+          <t>correct_answer_first_int_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question_type_choices</t>
+          <t>correct_answer_first_int_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>correct_answer_type_choices</t>
+          <t>correct_answer_first_int_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>correct_answer_type_choices</t>
+          <t>question_type_first_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>integer_comparison</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Integer Comparison</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>correct_answer_choices</t>
+          <t>question_type_first_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>not_integer_comparison</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not Integer Comparison</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>correct_answer_choices</t>
+          <t>correct_answer_type_first_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>same</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Same</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>submit_choices</t>
+          <t>correct_answer_type_first_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>different</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Different</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>submit_choices</t>
+          <t>compare_third_int_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>very_similar</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Very Similar</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>feedback_choices</t>
+          <t>compare_third_int_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>somewhat_similar</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Somewhat Similar</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>feedback_choices</t>
+          <t>compare_third_int_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>not_similar</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not Similar</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>correct_question_type_choices</t>
+          <t>compare_fourth_int_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>very_similar</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Very Similar</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>correct_question_type_choices</t>
+          <t>compare_fourth_int_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>somewhat_similar</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Somewhat Similar</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>compare_fourth_int_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>not_similar</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Not Similar</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>correct_answer_fourth_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>correct_answer_fourth_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>correct_answer_fourth_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>question_type_fourth_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>integer_comparison</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Integer Comparison</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>question_type_fourth_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>not_integer_comparison</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Not Integer Comparison</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>correct_answer_type_fourth_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Same</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>correct_answer_type_fourth_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>different</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Different</t>
         </is>
       </c>
     </row>
